--- a/artfynd/A 34739-2026 artfynd.xlsx
+++ b/artfynd/A 34739-2026 artfynd.xlsx
@@ -1697,7 +1697,7 @@
         <v>136042857</v>
       </c>
       <c r="B11" t="n">
-        <v>99377</v>
+        <v>99380</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>

--- a/artfynd/A 34739-2026 artfynd.xlsx
+++ b/artfynd/A 34739-2026 artfynd.xlsx
@@ -1697,7 +1697,7 @@
         <v>136042857</v>
       </c>
       <c r="B11" t="n">
-        <v>99380</v>
+        <v>99381</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>

--- a/artfynd/A 34739-2026 artfynd.xlsx
+++ b/artfynd/A 34739-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ12"/>
+  <dimension ref="A1:AZ13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1805,32 +1805,32 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>136042859</v>
+        <v>137282884</v>
       </c>
       <c r="B12" t="n">
-        <v>80064</v>
+        <v>99394</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>229821</v>
+        <v>220787</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
@@ -1844,13 +1844,13 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>541903</v>
+        <v>541911</v>
       </c>
       <c r="R12" t="n">
-        <v>6875093</v>
+        <v>6875015</v>
       </c>
       <c r="S12" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1874,12 +1874,22 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="Z12" t="inlineStr">
+        <is>
+          <t>09:17</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="AB12" t="inlineStr">
+        <is>
+          <t>09:17</t>
         </is>
       </c>
       <c r="AC12" t="inlineStr">
@@ -1909,6 +1919,117 @@
       </c>
       <c r="AY12" t="inlineStr"/>
       <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137282884</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>136042859</v>
+      </c>
+      <c r="B13" t="n">
+        <v>80064</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>229821</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Vedflamlav</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Ramboldia elabens</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Hennan, Hls</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>541903</v>
+      </c>
+      <c r="R13" t="n">
+        <v>6875093</v>
+      </c>
+      <c r="S13" t="n">
+        <v>10</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Hälsingland</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/136042859</t>
         </is>
@@ -1927,6 +2048,7 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 34739-2026 artfynd.xlsx
+++ b/artfynd/A 34739-2026 artfynd.xlsx
@@ -1808,7 +1808,7 @@
         <v>137282884</v>
       </c>
       <c r="B12" t="n">
-        <v>99394</v>
+        <v>99404</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>

--- a/artfynd/A 34739-2026 artfynd.xlsx
+++ b/artfynd/A 34739-2026 artfynd.xlsx
@@ -1808,7 +1808,7 @@
         <v>137282884</v>
       </c>
       <c r="B12" t="n">
-        <v>99404</v>
+        <v>99405</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>

--- a/artfynd/A 34739-2026 artfynd.xlsx
+++ b/artfynd/A 34739-2026 artfynd.xlsx
@@ -1808,7 +1808,7 @@
         <v>137282884</v>
       </c>
       <c r="B12" t="n">
-        <v>99405</v>
+        <v>99410</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>

--- a/artfynd/A 34739-2026 artfynd.xlsx
+++ b/artfynd/A 34739-2026 artfynd.xlsx
@@ -1808,7 +1808,7 @@
         <v>137282884</v>
       </c>
       <c r="B12" t="n">
-        <v>99410</v>
+        <v>99412</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>

--- a/artfynd/A 34739-2026 artfynd.xlsx
+++ b/artfynd/A 34739-2026 artfynd.xlsx
@@ -1808,7 +1808,7 @@
         <v>137282884</v>
       </c>
       <c r="B12" t="n">
-        <v>99412</v>
+        <v>99418</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>

--- a/artfynd/A 34739-2026 artfynd.xlsx
+++ b/artfynd/A 34739-2026 artfynd.xlsx
@@ -1808,7 +1808,7 @@
         <v>137282884</v>
       </c>
       <c r="B12" t="n">
-        <v>99418</v>
+        <v>99430</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>

--- a/artfynd/A 34739-2026 artfynd.xlsx
+++ b/artfynd/A 34739-2026 artfynd.xlsx
@@ -1808,7 +1808,7 @@
         <v>137282884</v>
       </c>
       <c r="B12" t="n">
-        <v>99430</v>
+        <v>99431</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>

--- a/artfynd/A 34739-2026 artfynd.xlsx
+++ b/artfynd/A 34739-2026 artfynd.xlsx
@@ -1808,7 +1808,7 @@
         <v>137282884</v>
       </c>
       <c r="B12" t="n">
-        <v>99431</v>
+        <v>99434</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>

--- a/artfynd/A 34739-2026 artfynd.xlsx
+++ b/artfynd/A 34739-2026 artfynd.xlsx
@@ -1808,7 +1808,7 @@
         <v>137282884</v>
       </c>
       <c r="B12" t="n">
-        <v>99434</v>
+        <v>99438</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
